--- a/data/trans_orig/IP05A04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A04-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>43564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50484</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51616</t>
+          <t>52125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58043</t>
+          <t>58048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97991</t>
+          <t>98063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107046</t>
+          <t>107181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71964</t>
+          <t>72906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85063</t>
+          <t>85872</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73882</t>
+          <t>73257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88754</t>
+          <t>88333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150871</t>
+          <t>151217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170555</t>
+          <t>170474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27466</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50492</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>65134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69719</t>
+          <t>69722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133010</t>
+          <t>133002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66181</t>
+          <t>66170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72667</t>
+          <t>72676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140583</t>
+          <t>141033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148679</t>
+          <t>148781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33764</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>49492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63642</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>47679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53935</t>
+          <t>53946</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52954</t>
+          <t>53496</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58455</t>
+          <t>58453</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>103735</t>
+          <t>103102</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>111652</t>
+          <t>111672</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120208</t>
+          <t>120135</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126586</t>
+          <t>126557</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>123219</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131051</t>
+          <t>131029</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>246448</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>256289</t>
+          <t>256783</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>111426</t>
+          <t>111446</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>127003</t>
+          <t>127320</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135934</t>
+          <t>136566</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>149551</t>
+          <t>149691</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>252971</t>
+          <t>252579</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>273372</t>
+          <t>273040</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>37316</t>
+          <t>37557</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>55670</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>487</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>573912</t>
+          <t>574508</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>623553</t>
+          <t>623906</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>650370</t>
+          <t>650920</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1208496</t>
+          <t>1208356</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1248268</t>
+          <t>1245957</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>59322</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>116951</t>
+          <t>116636</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>152062</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50970</t>
+          <t>51511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56238</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>57716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64196</t>
+          <t>64168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111983</t>
+          <t>111787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119665</t>
+          <t>120175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84948</t>
+          <t>85071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96083</t>
+          <t>96141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82916</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97142</t>
+          <t>97768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173742</t>
+          <t>173256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190798</t>
+          <t>190808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>22178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62819</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63710</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69918</t>
+          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129384</t>
+          <t>129588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137280</t>
+          <t>137326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75689</t>
+          <t>75721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76209</t>
+          <t>75905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148570</t>
+          <t>148729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156111</t>
+          <t>156282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37207</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26065</t>
+          <t>25934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36519</t>
+          <t>36557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>56631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70876</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28199</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51867</t>
+          <t>51802</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52071</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106075</t>
+          <t>107045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114044</t>
+          <t>114334</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>141119</t>
+          <t>140926</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>138127</t>
+          <t>138326</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>151051</t>
+          <t>151127</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>143896</t>
+          <t>145254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>158042</t>
+          <t>158437</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>286636</t>
+          <t>287303</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>305689</t>
+          <t>306036</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>41278</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>646380</t>
+          <t>646724</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>667901</t>
+          <t>667802</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>672015</t>
+          <t>671651</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>697058</t>
+          <t>697178</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1325130</t>
+          <t>1323890</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1360383</t>
+          <t>1358863</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>75769</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>107377</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>45692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53348</t>
+          <t>53287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>52898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61229</t>
+          <t>60945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>101809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112506</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65649</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79717</t>
+          <t>81265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76112</t>
+          <t>75112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90567</t>
+          <t>90162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145208</t>
+          <t>145430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166343</t>
+          <t>167487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41170</t>
+          <t>41794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60966</t>
+          <t>60860</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66120</t>
+          <t>66116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60121</t>
+          <t>60050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67114</t>
+          <t>67074</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123450</t>
+          <t>124148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132491</t>
+          <t>132516</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72580</t>
+          <t>72544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70707</t>
+          <t>70746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77750</t>
+          <t>77694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145878</t>
+          <t>145752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153069</t>
+          <t>153011</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>33613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68774</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>80392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>16704</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50076</t>
+          <t>49735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51200</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57018</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>103518</t>
+          <t>103756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110581</t>
+          <t>110272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>113831</t>
+          <t>114037</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125679</t>
+          <t>126075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121192</t>
+          <t>119900</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133998</t>
+          <t>133565</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>239788</t>
+          <t>240171</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>257298</t>
+          <t>257547</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21574</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37174</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153748</t>
+          <t>153955</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161133</t>
+          <t>161249</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159798</t>
+          <t>159352</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>167419</t>
+          <t>167507</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>317034</t>
+          <t>316638</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>327632</t>
+          <t>327235</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>619370</t>
+          <t>620090</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>644709</t>
+          <t>643246</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>652796</t>
+          <t>651138</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>679181</t>
+          <t>678489</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1279691</t>
+          <t>1280034</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1315677</t>
+          <t>1316402</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>64958</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>83754</t>
+          <t>82953</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112570</t>
+          <t>112680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123791</t>
+          <t>123623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104149</t>
+          <t>104465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118663</t>
+          <t>118379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>220797</t>
+          <t>220534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240365</t>
+          <t>240556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29613</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52350</t>
+          <t>52712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>57734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57378</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64836</t>
+          <t>64982</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112874</t>
+          <t>113065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121388</t>
+          <t>121583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64472</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69988</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69572</t>
+          <t>69976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77599</t>
+          <t>77601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138244</t>
+          <t>138566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146966</t>
+          <t>147110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68272</t>
+          <t>68218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>73932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40492</t>
+          <t>40862</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>45276</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53964</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95492</t>
+          <t>95587</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>100720</t>
+          <t>100643</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>107595</t>
+          <t>107528</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118177</t>
+          <t>118041</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>136760</t>
+          <t>136585</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148966</t>
+          <t>148603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>248493</t>
+          <t>248669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>264743</t>
+          <t>264470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>127465</t>
+          <t>127492</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>151928</t>
+          <t>151758</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>156441</t>
+          <t>156433</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>280542</t>
+          <t>281367</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>286764</t>
+          <t>286861</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>625845</t>
+          <t>625985</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>643144</t>
+          <t>643683</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>711773</t>
+          <t>711808</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>734682</t>
+          <t>734022</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1345484</t>
+          <t>1344876</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1372326</t>
+          <t>1373396</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,82 +17642,82 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>9633</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>16972</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>9633</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>5229</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>17143</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>11695</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>27136</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>18039</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>11517</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
